--- a/申請カード.xlsx
+++ b/申請カード.xlsx
@@ -10,7 +10,7 @@
     <sheet name="申請カード" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'申請カード'!$A$1:$E$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'申請カード'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,17 +29,16 @@
     </font>
     <font>
       <name val="ＭＳ Ｐゴシック"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
       <b val="1"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="ＭＳ Ｐゴシック"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="ＭＳ Ｐゴシック"/>
-      <b val="1"/>
-      <sz val="11"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="2">
@@ -50,13 +49,30 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border diagonalDown="1">
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal style="thin">
+        <color rgb="00000000"/>
+      </diagonal>
     </border>
     <border>
       <left style="thin">
@@ -76,27 +92,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -464,182 +486,208 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:E26"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20.5" customWidth="1" min="2" max="2"/>
+    <col width="20.5" customWidth="1" min="3" max="3"/>
+    <col width="20.5" customWidth="1" min="4" max="4"/>
+    <col width="20.5" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="10" customHeight="1"/>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(有休･振休･欠勤･休暇)申請カード　</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="ＭＳ Ｐゴシック"/>
+              <b val="1"/>
+              <sz val="20"/>
+            </rPr>
+            <t>(有休･振休･欠勤･休暇)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="ＭＳ Ｐゴシック"/>
+              <b val="1"/>
+              <sz val="36"/>
+            </rPr>
+            <t xml:space="preserve">申請カード　</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>↑該当する場所に〇を付けてください。　　　　　　　　　　　提出日：　　　年　 　月　 　日</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="ＭＳ Ｐゴシック"/>
+              <sz val="12"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">申請者：　　　　　　　　　　　</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="ＭＳ Ｐゴシック"/>
+              <sz val="12"/>
+            </rPr>
+            <t>　　　　</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="ＭＳ Ｐゴシック"/>
+              <sz val="12"/>
+              <u val="single"/>
+            </rPr>
+            <t>有休申請日：　　　年　　　月　　　日</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="ＭＳ Ｐゴシック"/>
-              <sz val="11"/>
+              <sz val="12"/>
               <u val="single"/>
             </rPr>
-            <t xml:space="preserve">申請者：　　　　　　　　　　　</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="ＭＳ Ｐゴシック"/>
-              <sz val="11"/>
-            </rPr>
-            <t>　　　　</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="ＭＳ Ｐゴシック"/>
-              <sz val="11"/>
+            <t xml:space="preserve">日にち移動可否：　　　　　　可　　　/　　　　不可　　　　　　　　　　　　</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="ＭＳ Ｐゴシック"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">有休申請の際は、このカードを課長へ提出してください。　　</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="ＭＳ Ｐゴシック"/>
+              <sz val="12"/>
               <u val="single"/>
             </rPr>
-            <t>有休申請日：　　　年　　　月　　　日</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="ＭＳ Ｐゴシック"/>
-              <sz val="11"/>
-              <u val="single"/>
-            </rPr>
-            <t xml:space="preserve">日にち移動可否：　　　　　　可　　　/　　　　不可　　　　　　　　　　　　</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="ＭＳ Ｐゴシック"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">有休申請の際は、このカードを課長へ提出してください。　　</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="ＭＳ Ｐゴシック"/>
-              <sz val="11"/>
-              <u val="single"/>
-            </rPr>
             <t xml:space="preserve">弁当注文者：　　要　　／　　不要　　　</t>
           </r>
         </is>
       </c>
     </row>
-    <row r="7" ht="10" customHeight="1"/>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="4" t="inlineStr"/>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>品質課長</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>副社長</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>社長</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>総務</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="84" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>①品質課長</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>②副社長</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>③社長</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>④総務</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="74" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>承認欄</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10" ht="92" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="74" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>処理内容</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr"/>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>※生産計画への反映</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>※有休管理表への記入
 ※お弁当の処理</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="10" customHeight="1"/>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>株式会社　原マシナリー</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="14" customHeight="1"/>
-    <row r="14" ht="14" customHeight="1"/>
-    <row r="15" ht="10" customHeight="1"/>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(有休･振休･欠勤･休暇)申請カード　</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="10" ht="22" customHeight="1"/>
+    <row r="11" ht="22" customHeight="1"/>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="ＭＳ Ｐゴシック"/>
+              <b val="1"/>
+              <sz val="20"/>
+            </rPr>
+            <t>(有休･振休･欠勤･休暇)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="ＭＳ Ｐゴシック"/>
+              <b val="1"/>
+              <sz val="36"/>
+            </rPr>
+            <t xml:space="preserve">申請カード　</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>↑該当する場所に〇を付けてください。　　　　　　　　　　　提出日：　　　年　 　月　 　日</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="ＭＳ Ｐゴシック"/>
-              <sz val="11"/>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="ＭＳ Ｐゴシック"/>
+              <sz val="12"/>
               <u val="single"/>
             </rPr>
             <t xml:space="preserve">申請者：　　　　　　　　　　　</t>
@@ -647,14 +695,14 @@
           <r>
             <rPr>
               <rFont val="ＭＳ Ｐゴシック"/>
-              <sz val="11"/>
+              <sz val="12"/>
             </rPr>
             <t>　　　　</t>
           </r>
           <r>
             <rPr>
               <rFont val="ＭＳ Ｐゴシック"/>
-              <sz val="11"/>
+              <sz val="12"/>
               <u val="single"/>
             </rPr>
             <t>有休申請日：　　　年　　　月　　　日</t>
@@ -662,13 +710,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="ＭＳ Ｐゴシック"/>
-              <sz val="11"/>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="ＭＳ Ｐゴシック"/>
+              <sz val="12"/>
               <u val="single"/>
             </rPr>
             <t xml:space="preserve">日にち移動可否：　　　　　　可　　　/　　　　不可　　　　　　　　　　　　</t>
@@ -676,20 +724,20 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="ＭＳ Ｐゴシック"/>
-              <sz val="11"/>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="ＭＳ Ｐゴシック"/>
+              <sz val="12"/>
             </rPr>
             <t xml:space="preserve">有休申請の際は、このカードを課長へ提出してください。　　</t>
           </r>
           <r>
             <rPr>
               <rFont val="ＭＳ Ｐゴシック"/>
-              <sz val="11"/>
+              <sz val="12"/>
               <u val="single"/>
             </rPr>
             <t xml:space="preserve">弁当注文者：　　要　　／　　不要　　　</t>
@@ -697,64 +745,62 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="10" customHeight="1"/>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="4" t="inlineStr"/>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>品質課長</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>副社長</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>社長</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>総務</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="84" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>①品質課長</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>②副社長</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>③社長</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>④総務</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="74" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>承認欄</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr"/>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24" ht="92" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr"/>
+      <c r="C18" s="6" t="inlineStr"/>
+      <c r="D18" s="6" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="74" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>処理内容</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr"/>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>※生産計画への反映</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>※有休管理表への記入
 ※お弁当の処理</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="10" customHeight="1"/>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>株式会社　原マシナリー</t>
         </is>
@@ -765,18 +811,18 @@
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A9:E9"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0" footer="0"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageMargins left="0.45" right="0.45" top="0.25" bottom="0.25" header="0" footer="0"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>